--- a/ig/DM-OCTOBRE-2025/ValueSet-JDV-J05-SubjectRole-CISIS.xlsx
+++ b/ig/DM-OCTOBRE-2025/ValueSet-JDV-J05-SubjectRole-CISIS.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="921">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="923">
   <si>
     <t>Property</t>
   </si>
@@ -2348,6 +2348,12 @@
   </si>
   <si>
     <t>Pharmacien remplaçant Bonnes Pratiques de Dispensation d'Oxygène</t>
+  </si>
+  <si>
+    <t>FON-62</t>
+  </si>
+  <si>
+    <t>Consultations de solidarité territoriale</t>
   </si>
   <si>
     <t>FON-AU</t>
@@ -3181,7 +3187,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -3518,18 +3524,26 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>38</v>
+        <v>777</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>38</v>
+        <v>778</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
         <v>39</v>
       </c>
-      <c r="B43" t="s" s="2">
-        <v>777</v>
+      <c r="B44" t="s" s="2">
+        <v>779</v>
       </c>
     </row>
   </sheetData>
@@ -3556,570 +3570,570 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>793</v>
+        <v>795</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>797</v>
+        <v>799</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>803</v>
+        <v>805</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>805</v>
+        <v>807</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>807</v>
+        <v>809</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>809</v>
+        <v>811</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>813</v>
+        <v>815</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>821</v>
+        <v>823</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>829</v>
+        <v>831</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>835</v>
+        <v>837</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>839</v>
+        <v>841</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>841</v>
+        <v>843</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>843</v>
+        <v>845</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>847</v>
+        <v>849</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>849</v>
+        <v>851</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>853</v>
+        <v>855</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>855</v>
+        <v>857</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>857</v>
+        <v>859</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>859</v>
+        <v>861</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>861</v>
+        <v>863</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>863</v>
+        <v>865</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>865</v>
+        <v>867</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>867</v>
+        <v>869</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>871</v>
+        <v>873</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>875</v>
+        <v>877</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>877</v>
+        <v>879</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>879</v>
+        <v>881</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>881</v>
+        <v>883</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>883</v>
+        <v>885</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>885</v>
+        <v>887</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>887</v>
+        <v>889</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>893</v>
+        <v>895</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>895</v>
+        <v>897</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>899</v>
+        <v>901</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>901</v>
+        <v>903</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>905</v>
+        <v>907</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>907</v>
+        <v>909</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>909</v>
+        <v>911</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>911</v>
+        <v>913</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>913</v>
+        <v>915</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>915</v>
+        <v>917</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>917</v>
+        <v>919</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>919</v>
+        <v>921</v>
       </c>
     </row>
     <row r="73">
@@ -4135,7 +4149,7 @@
         <v>39</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-OCTOBRE-2025/ValueSet-JDV-J05-SubjectRole-CISIS.xlsx
+++ b/ig/DM-OCTOBRE-2025/ValueSet-JDV-J05-SubjectRole-CISIS.xlsx
@@ -46,7 +46,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250721120000</t>
+    <t>20251028120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -73,7 +73,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-21T12:00:00+01:00</t>
+    <t>2025-10-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
